--- a/Excel/Hospitality_Booking_Revenue_Performa.xlsx
+++ b/Excel/Hospitality_Booking_Revenue_Performa.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nithinsaijatoth/Desktop/Hospitality-Booking-Revenue-Performance/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yogee\AppData\Local\Temp\portfolio_redesign_20261027\redesigned\Hospitality\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C93AD5A1-9EF2-2A43-9218-64C2F6E535C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A159F582-78F1-4023-BC82-205DBB0F4088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Dictionary" sheetId="2" r:id="rId1"/>
@@ -32,6 +32,7 @@
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="2" hidden="1">Cleaned_Motel_Booking_Data!$A$1:$P$121</definedName>
     <definedName name="NativeTimeline_Check_In_Date">#N/A</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">Excel_Dashboard!$A$1:$T$40</definedName>
     <definedName name="Slicer_Booking_Source">#N/A</definedName>
     <definedName name="Slicer_Guest_Country">#N/A</definedName>
     <definedName name="Slicer_Payment_Status">#N/A</definedName>
@@ -104,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="353">
   <si>
     <t>Booking_ID</t>
   </si>
@@ -793,9 +794,6 @@
     <t>Average of Guest_Rating</t>
   </si>
   <si>
-    <t>Motel Booking Analytics Dashboard</t>
-  </si>
-  <si>
     <t>Details for Sum of Estimated_Revenue_GBP</t>
   </si>
   <si>
@@ -1174,21 +1172,49 @@
   <si>
     <t>Revenue</t>
   </si>
+  <si>
+    <t>Hospitality | booking &amp; revenue performance</t>
+  </si>
+  <si>
+    <t>Management snapshot | estimated booking revenue in GBP | 120 cleaned booking records</t>
+  </si>
+  <si>
+    <t>Estimated revenue</t>
+  </si>
+  <si>
+    <t>Booking records</t>
+  </si>
+  <si>
+    <t>Completed bookings</t>
+  </si>
+  <si>
+    <t>Cancellation rate</t>
+  </si>
+  <si>
+    <t>Average guest rating</t>
+  </si>
+  <si>
+    <t>Explore booking segments</t>
+  </si>
+  <si>
+    <t>Revenue is estimated booking value, not cash receipts or profit. Cancelled bookings and no-shows are separate statuses. Ratings use available numeric responses.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
-    <numFmt numFmtId="44" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
-    <numFmt numFmtId="165" formatCode="\£#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="[$GBP]\ #,##0.00"/>
-    <numFmt numFmtId="168" formatCode="_-[$£-809]* #,##0.00_-;\-[$£-809]* #,##0.00_-;_-[$£-809]* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="mm/dd/yy"/>
+  <numFmts count="8">
+    <numFmt numFmtId="164" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
+    <numFmt numFmtId="166" formatCode="\£#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="[$GBP]\ #,##0.00"/>
+    <numFmt numFmtId="169" formatCode="_-[$£-809]* #,##0.00_-;\-[$£-809]* #,##0.00_-;_-[$£-809]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="mm/dd/yy"/>
+    <numFmt numFmtId="171" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1222,18 +1248,7 @@
     </font>
     <font>
       <b/>
-      <sz val="28"/>
-      <color theme="4"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22"/>
       <name val="Carlito"/>
     </font>
     <font>
@@ -1267,8 +1282,81 @@
       <sz val="9"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF263445"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF263445"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color rgb="FF263445"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF56687A"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF263445"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="23"/>
+      <color rgb="FF26715B"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="23"/>
+      <color rgb="FF2563A6"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="23"/>
+      <color rgb="FFA67723"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF56687A"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="23"/>
+      <color rgb="FF263445"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF263445"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1286,8 +1374,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F1EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF2F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F1E4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1422,19 +1534,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1443,81 +1564,172 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="20" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="19" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="18" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="166" fontId="22" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="22" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="6" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="22" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="22" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="22" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="22" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="22" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1572,10 +1784,19 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
+      <numFmt numFmtId="172" formatCode="dd/mm/yy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
+      <numFmt numFmtId="172" formatCode="dd/mm/yy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="172" formatCode="dd/mm/yy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="172" formatCode="dd/mm/yy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="172" formatCode="dd/mm/yy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1593,19 +1814,10 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
+      <numFmt numFmtId="172" formatCode="dd/mm/yy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1629,7 +1841,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1651,23 +1863,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+              <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="50000"/>
-                    <a:lumOff val="50000"/>
-                  </a:schemeClr>
+                  <a:srgbClr val="263445"/>
                 </a:solidFill>
-                <a:latin typeface="+mj-lt"/>
-                <a:ea typeface="+mj-ea"/>
-                <a:cs typeface="+mj-cs"/>
+                <a:latin typeface="Aptos"/>
+                <a:ea typeface="Aptos"/>
+                <a:cs typeface="Aptos"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN" sz="1600" b="1" i="0" u="none" strike="noStrike" cap="none" normalizeH="0" baseline="0"/>
-              <a:t>REVENUE BY ROOM TYPE</a:t>
+              <a:rPr lang="en-US"/>
+              <a:t>Estimated revenue by room type</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1684,16 +1892,13 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+            <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
+                <a:srgbClr val="263445"/>
               </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:ea typeface="+mj-ea"/>
-              <a:cs typeface="+mj-cs"/>
+              <a:latin typeface="Aptos"/>
+              <a:ea typeface="Aptos"/>
+              <a:cs typeface="Aptos"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -1785,10 +1990,12 @@
         <c:idx val="5"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:srgbClr val="26715B"/>
           </a:solidFill>
           <a:ln>
-            <a:noFill/>
+            <a:solidFill>
+              <a:srgbClr val="26715B"/>
+            </a:solidFill>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -1797,6 +2004,7 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:numFmt formatCode="\£#,##0" sourceLinked="0"/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1805,9 +2013,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -1818,9 +2024,9 @@
                       <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:latin typeface="Aptos"/>
+                  <a:ea typeface="Aptos"/>
+                  <a:cs typeface="Aptos"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -1871,15 +2077,18 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="26715B"/>
             </a:solidFill>
             <a:ln>
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="26715B"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:numFmt formatCode="\£#,##0" sourceLinked="0"/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -1888,9 +2097,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -1901,9 +2108,9 @@
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:latin typeface="Aptos"/>
+                    <a:ea typeface="Aptos"/>
+                    <a:cs typeface="Aptos"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -2054,9 +2261,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="Aptos"/>
+                <a:ea typeface="Aptos"/>
+                <a:cs typeface="Aptos"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -2080,17 +2287,14 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
+                <a:srgbClr val="E7ECE9"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="[$GBP]\ #,##0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="\£#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2113,9 +2317,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="Aptos"/>
+                <a:ea typeface="Aptos"/>
+                <a:cs typeface="Aptos"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -2148,14 +2352,11 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:srgbClr val="DDE5E0"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -2166,7 +2367,11 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="900">
+          <a:latin typeface="Aptos"/>
+          <a:ea typeface="Aptos"/>
+          <a:cs typeface="Aptos"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -2182,7 +2387,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -2197,7 +2401,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2772,7 +2976,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2794,23 +2998,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+              <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="50000"/>
-                    <a:lumOff val="50000"/>
-                  </a:schemeClr>
+                  <a:srgbClr val="263445"/>
                 </a:solidFill>
-                <a:latin typeface="+mj-lt"/>
-                <a:ea typeface="+mj-ea"/>
-                <a:cs typeface="+mj-cs"/>
+                <a:latin typeface="Aptos"/>
+                <a:ea typeface="Aptos"/>
+                <a:cs typeface="Aptos"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN" sz="1600" b="1" i="0" u="none" strike="noStrike" cap="none" normalizeH="0" baseline="0"/>
-              <a:t>BOOKINGS BY BOOKING SOURCE</a:t>
+              <a:rPr lang="en-US"/>
+              <a:t>Bookings by channel</a:t>
             </a:r>
-            <a:endParaRPr lang="en-GB"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -2835,16 +3035,13 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+            <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
+                <a:srgbClr val="263445"/>
               </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:ea typeface="+mj-ea"/>
-              <a:cs typeface="+mj-cs"/>
+              <a:latin typeface="Aptos"/>
+              <a:ea typeface="Aptos"/>
+              <a:cs typeface="Aptos"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-GB"/>
@@ -2934,10 +3131,12 @@
         <c:idx val="5"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:srgbClr val="2563A6"/>
           </a:solidFill>
           <a:ln>
-            <a:noFill/>
+            <a:solidFill>
+              <a:srgbClr val="2563A6"/>
+            </a:solidFill>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -2946,6 +3145,7 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:numFmt formatCode="0" sourceLinked="0"/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -2967,9 +3167,9 @@
                       <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:latin typeface="Aptos"/>
+                  <a:ea typeface="Aptos"/>
+                  <a:cs typeface="Aptos"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -3020,15 +3220,18 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="2563A6"/>
             </a:solidFill>
             <a:ln>
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2563A6"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:numFmt formatCode="0" sourceLinked="0"/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -3050,9 +3253,9 @@
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:latin typeface="Aptos"/>
+                    <a:ea typeface="Aptos"/>
+                    <a:cs typeface="Aptos"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -3202,9 +3405,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="Aptos"/>
+                <a:ea typeface="Aptos"/>
+                <a:cs typeface="Aptos"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -3228,14 +3431,14 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:srgbClr val="E7ECE9"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3258,9 +3461,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="Aptos"/>
+                <a:ea typeface="Aptos"/>
+                <a:cs typeface="Aptos"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -3293,14 +3496,11 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:srgbClr val="DDE5E0"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -3311,7 +3511,11 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="900">
+          <a:latin typeface="Aptos"/>
+          <a:ea typeface="Aptos"/>
+          <a:cs typeface="Aptos"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -3327,7 +3531,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -3342,7 +3545,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3364,23 +3567,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
+              <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="50000"/>
-                    <a:lumOff val="50000"/>
-                  </a:schemeClr>
+                  <a:srgbClr val="263445"/>
                 </a:solidFill>
-                <a:latin typeface="+mj-lt"/>
-                <a:ea typeface="+mj-ea"/>
-                <a:cs typeface="+mj-cs"/>
+                <a:latin typeface="Aptos"/>
+                <a:ea typeface="Aptos"/>
+                <a:cs typeface="Aptos"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN" sz="1600" b="1" i="0" u="none" strike="noStrike" normalizeH="0" baseline="0"/>
-              <a:t>BOOKINGS BY STATUS</a:t>
+              <a:rPr lang="en-US"/>
+              <a:t>Completed, cancelled &amp; no-show</a:t>
             </a:r>
-            <a:endParaRPr lang="en-GB"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -3397,16 +3596,13 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
+            <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
+                <a:srgbClr val="263445"/>
               </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:ea typeface="+mj-ea"/>
-              <a:cs typeface="+mj-cs"/>
+              <a:latin typeface="Aptos"/>
+              <a:ea typeface="Aptos"/>
+              <a:cs typeface="Aptos"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-GB"/>
@@ -3541,23 +3737,12 @@
       <c:pivotFmt>
         <c:idx val="13"/>
         <c:spPr>
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
+          <a:solidFill>
+            <a:srgbClr val="A67723"/>
+          </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
-              <a:schemeClr val="lt1"/>
+              <a:srgbClr val="A67723"/>
             </a:solidFill>
           </a:ln>
           <a:effectLst/>
@@ -3567,6 +3752,7 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:numFmt formatCode="0" sourceLinked="0"/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -3588,19 +3774,19 @@
                       <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:latin typeface="Aptos"/>
+                  <a:ea typeface="Aptos"/>
+                  <a:cs typeface="Aptos"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
+          <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
@@ -3610,23 +3796,12 @@
       <c:pivotFmt>
         <c:idx val="14"/>
         <c:spPr>
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
+          <a:solidFill>
+            <a:srgbClr val="A67723"/>
+          </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
-              <a:schemeClr val="lt1"/>
+              <a:srgbClr val="A67723"/>
             </a:solidFill>
           </a:ln>
           <a:effectLst/>
@@ -3635,23 +3810,12 @@
       <c:pivotFmt>
         <c:idx val="15"/>
         <c:spPr>
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
+          <a:solidFill>
+            <a:srgbClr val="A67723"/>
+          </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
-              <a:schemeClr val="lt1"/>
+              <a:srgbClr val="A67723"/>
             </a:solidFill>
           </a:ln>
           <a:effectLst/>
@@ -3660,23 +3824,12 @@
       <c:pivotFmt>
         <c:idx val="16"/>
         <c:spPr>
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
+          <a:solidFill>
+            <a:srgbClr val="A67723"/>
+          </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
-              <a:schemeClr val="lt1"/>
+              <a:srgbClr val="A67723"/>
             </a:solidFill>
           </a:ln>
           <a:effectLst/>
@@ -3685,8 +3838,10 @@
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
-      <c:doughnutChart>
-        <c:varyColors val="1"/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -3701,27 +3856,29 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="A67723"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="A67723"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
           <c:dPt>
             <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="60000"/>
-                      <a:lumOff val="40000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1"/>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:srgbClr val="A67723"/>
+              </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
-                  <a:schemeClr val="lt1"/>
+                  <a:srgbClr val="A67723"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -3734,25 +3891,15 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent2">
-                      <a:lumMod val="60000"/>
-                      <a:lumOff val="40000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent2"/>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:srgbClr val="A67723"/>
+              </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
-                  <a:schemeClr val="lt1"/>
+                  <a:srgbClr val="A67723"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -3765,25 +3912,15 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent3">
-                      <a:lumMod val="60000"/>
-                      <a:lumOff val="40000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent3"/>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:srgbClr val="A67723"/>
+              </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
-                  <a:schemeClr val="lt1"/>
+                  <a:srgbClr val="A67723"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -3795,6 +3932,7 @@
             </c:extLst>
           </c:dPt>
           <c:dLbls>
+            <c:numFmt formatCode="0" sourceLinked="0"/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -3816,37 +3954,39 @@
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:latin typeface="Aptos"/>
+                    <a:ea typeface="Aptos"/>
+                    <a:cs typeface="Aptos"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
+            <c:showVal val="1"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
-            <c:showPercent val="1"/>
+            <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                  <a:solidFill>
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="35000"/>
-                      <a:lumOff val="65000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:round/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
@@ -3895,13 +4035,111 @@
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
+          <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:firstSliceAng val="0"/>
-        <c:holeSize val="70"/>
-      </c:doughnutChart>
+        <c:gapWidth val="100"/>
+        <c:axId val="143184047"/>
+        <c:axId val="70787535"/>
+      </c:barChart>
+      <c:valAx>
+        <c:axId val="70787535"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:srgbClr val="E7ECE9"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Aptos"/>
+                <a:ea typeface="Aptos"/>
+                <a:cs typeface="Aptos"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="143184047"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="143184047"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Aptos"/>
+                <a:ea typeface="Aptos"/>
+                <a:cs typeface="Aptos"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="70787535"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -3910,41 +4148,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -3958,14 +4161,11 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:srgbClr val="DDE5E0"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -3976,7 +4176,11 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="900">
+          <a:latin typeface="Aptos"/>
+          <a:ea typeface="Aptos"/>
+          <a:cs typeface="Aptos"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -3992,8 +4196,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -4008,7 +4210,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4030,23 +4232,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:srgbClr val="263445"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="Aptos"/>
+                <a:ea typeface="Aptos"/>
+                <a:cs typeface="Aptos"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN"/>
-              <a:t>MONTHLY REVENUE TREND</a:t>
+              <a:rPr lang="en-US"/>
+              <a:t>Monthly estimated booking revenue</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -4063,16 +4261,13 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+            <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:srgbClr val="263445"/>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:latin typeface="Aptos"/>
+              <a:ea typeface="Aptos"/>
+              <a:cs typeface="Aptos"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -4132,25 +4327,26 @@
       <c:pivotFmt>
         <c:idx val="4"/>
         <c:spPr>
-          <a:ln w="22225" cap="rnd">
+          <a:ln w="25400" cap="rnd">
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="26715B"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="26715B"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln w="25400">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="26715B"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -4179,9 +4375,9 @@
                       <a:lumOff val="50000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:latin typeface="Aptos"/>
+                  <a:ea typeface="Aptos"/>
+                  <a:cs typeface="Aptos"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -4219,25 +4415,26 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="22225" cap="rnd">
+            <a:ln w="25400" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="26715B"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="6"/>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="26715B"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln w="25400">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:srgbClr val="26715B"/>
                 </a:solidFill>
+                <a:prstDash val="solid"/>
                 <a:round/>
               </a:ln>
               <a:effectLst/>
@@ -4395,16 +4592,16 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="Aptos"/>
+                <a:ea typeface="Aptos"/>
+                <a:cs typeface="Aptos"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -4424,7 +4621,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:numFmt formatCode="[$GBP]\ #,##0" sourceLinked="0"/>
+        <c:numFmt formatCode="\£#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4453,9 +4650,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="Aptos"/>
+                <a:ea typeface="Aptos"/>
+                <a:cs typeface="Aptos"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -4486,14 +4683,11 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:srgbClr val="DDE5E0"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -4504,7 +4698,11 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="900">
+          <a:latin typeface="Aptos"/>
+          <a:ea typeface="Aptos"/>
+          <a:cs typeface="Aptos"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -4520,7 +4718,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -4535,7 +4732,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4557,23 +4754,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+              <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="50000"/>
-                    <a:lumOff val="50000"/>
-                  </a:schemeClr>
+                  <a:srgbClr val="263445"/>
                 </a:solidFill>
-                <a:latin typeface="+mj-lt"/>
-                <a:ea typeface="+mj-ea"/>
-                <a:cs typeface="+mj-cs"/>
+                <a:latin typeface="Aptos"/>
+                <a:ea typeface="Aptos"/>
+                <a:cs typeface="Aptos"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN"/>
-              <a:t>AVERAGE RATING BY ROOM TYPE</a:t>
+              <a:rPr lang="en-US"/>
+              <a:t>Guest rating by room type</a:t>
             </a:r>
-            <a:endParaRPr lang="en-GB"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -4590,16 +4783,13 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+            <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
+                <a:srgbClr val="263445"/>
               </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:ea typeface="+mj-ea"/>
-              <a:cs typeface="+mj-cs"/>
+              <a:latin typeface="Aptos"/>
+              <a:ea typeface="Aptos"/>
+              <a:cs typeface="Aptos"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-GB"/>
@@ -4676,10 +4866,12 @@
         <c:idx val="4"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:srgbClr val="2563A6"/>
           </a:solidFill>
           <a:ln>
-            <a:noFill/>
+            <a:solidFill>
+              <a:srgbClr val="2563A6"/>
+            </a:solidFill>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -4688,6 +4880,7 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:numFmt formatCode="0.00" sourceLinked="0"/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -4709,9 +4902,9 @@
                       <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:latin typeface="Aptos"/>
+                  <a:ea typeface="Aptos"/>
+                  <a:cs typeface="Aptos"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -4752,15 +4945,18 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="2563A6"/>
             </a:solidFill>
             <a:ln>
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2563A6"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:numFmt formatCode="0.00" sourceLinked="0"/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -4782,9 +4978,9 @@
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:latin typeface="Aptos"/>
+                    <a:ea typeface="Aptos"/>
+                    <a:cs typeface="Aptos"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -4934,9 +5130,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="Aptos"/>
+                <a:ea typeface="Aptos"/>
+                <a:cs typeface="Aptos"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -4953,6 +5149,8 @@
         <c:axId val="1645751232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="5"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -4960,17 +5158,14 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
+                <a:srgbClr val="E7ECE9"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4993,9 +5188,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="Aptos"/>
+                <a:ea typeface="Aptos"/>
+                <a:cs typeface="Aptos"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -5028,14 +5223,11 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:srgbClr val="DDE5E0"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -5046,7 +5238,11 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="900">
+          <a:latin typeface="Aptos"/>
+          <a:ea typeface="Aptos"/>
+          <a:cs typeface="Aptos"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -5062,7 +5258,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -5077,7 +5272,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5711,7 +5906,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6378,7 +6573,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7277,7 +7472,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -13540,16 +13735,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>276246</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>88897</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>482600</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>162793</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>9875</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>22225</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13578,16 +13773,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>591828</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>88897</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>478375</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>9875</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13616,16 +13811,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>408801</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>143306</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>546100</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>295348</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>64284</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>3175</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13654,16 +13849,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>258457</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>143306</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>145004</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>64284</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>22225</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13692,16 +13887,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>532966</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>139935</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>206375</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>419513</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>55873</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13730,19 +13925,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>435704</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>29484</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>625475</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>275966</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>105424</xdr:rowOff>
+      <xdr:colOff>231775</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="7" name="Room_Type">
@@ -13765,7 +13960,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -13775,8 +13970,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12881704" y="1519617"/>
-              <a:ext cx="1499729" cy="2311140"/>
+              <a:off x="10094446" y="1901078"/>
+              <a:ext cx="2519829" cy="1046629"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -13795,7 +13990,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100"/>
+                <a:rPr lang="en-IN" sz="1100"/>
                 <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
 If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
               </a:r>
@@ -13808,19 +14003,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>611586</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>29484</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>625475</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>53975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>704659</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>231775</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>105424</xdr:rowOff>
+      <xdr:rowOff>92075</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="8" name="Booking_Source">
@@ -13843,7 +14038,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -13853,8 +14048,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="14717053" y="1519617"/>
-              <a:ext cx="1752539" cy="2311140"/>
+              <a:off x="10094446" y="3045946"/>
+              <a:ext cx="2519829" cy="1046629"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -13873,7 +14068,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100"/>
+                <a:rPr lang="en-IN" sz="1100"/>
                 <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
 If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
               </a:r>
@@ -13886,19 +14081,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>223851</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>29484</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>625475</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>22225</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>316923</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>114371</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>231775</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>60325</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="9" name="Payment_Status 1">
@@ -13921,7 +14116,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -13931,8 +14126,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="16818518" y="1519617"/>
-              <a:ext cx="1752538" cy="2320087"/>
+              <a:off x="10094446" y="4190813"/>
+              <a:ext cx="2519829" cy="1046630"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -13951,7 +14146,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100"/>
+                <a:rPr lang="en-IN" sz="1100"/>
                 <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
 If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
               </a:r>
@@ -13964,19 +14159,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>652544</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>29484</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>625475</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>734187</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>112960</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>231775</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="10" name="Guest_Country">
@@ -13999,7 +14194,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -14009,8 +14204,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="18906677" y="1519617"/>
-              <a:ext cx="1741110" cy="2318676"/>
+              <a:off x="10094446" y="5339043"/>
+              <a:ext cx="2519829" cy="1043267"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -14029,7 +14224,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100"/>
+                <a:rPr lang="en-IN" sz="1100"/>
                 <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
 If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
               </a:r>
@@ -14042,19 +14237,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>209515</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>36464</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>625475</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>130175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>252618</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>126171</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>231775</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>136525</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
-      <mc:Choice Requires="tsle">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="11" name="Check_In_Date 1">
@@ -14072,12 +14267,12 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
-              <tsle:timeslicer name="Check_In_Date 1"/>
+              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Check_In_Date 1"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -14087,8 +14282,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="15144715" y="4506864"/>
-              <a:ext cx="3362036" cy="1207307"/>
+              <a:off x="10094446" y="6483910"/>
+              <a:ext cx="2519829" cy="846791"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -14107,7 +14302,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100"/>
+                <a:rPr lang="en-IN" sz="1100"/>
                 <a:t>Timeline: Works in Excel 2013 or higher. Do not move or resize.</a:t>
               </a:r>
             </a:p>
@@ -14395,10 +14590,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14992,6 +15183,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition pivotCacheId="1983970043"/>
+    </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -17358,7 +17552,7 @@
   <dataFields count="1">
     <dataField name="Average of Guest_Rating" fld="11" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
   </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -17606,7 +17800,7 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -17824,7 +18018,7 @@
   <dataFields count="1">
     <dataField name="Count of Booking_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -18042,7 +18236,7 @@
   <dataFields count="1">
     <dataField name="Count of Booking_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -18250,7 +18444,7 @@
   <dataFields count="1">
     <dataField name="Count of Booking_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -18458,7 +18652,7 @@
   <dataFields count="1">
     <dataField name="Sum of Estimated_Revenue_GBP" fld="15" baseField="0" baseItem="0"/>
   </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -19057,7 +19251,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Estimated_Revenue_GBP" fld="15" baseField="0" baseItem="0" numFmtId="167"/>
+    <dataField name="Sum of Estimated_Revenue_GBP" fld="15" baseField="0" baseItem="0" numFmtId="168"/>
   </dataFields>
   <chartFormats count="2">
     <chartFormat chart="7" format="3" series="1">
@@ -19079,7 +19273,7 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -19700,7 +19894,7 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -20394,7 +20588,7 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -21036,7 +21230,7 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -21236,20 +21430,20 @@
     <sortCondition descending="1" ref="P1:P121"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{9C640707-0896-2C4E-B912-C7198DB41FE0}" uniqueName="1" name="Booking_ID" queryTableFieldId="1" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{0FAAFBDC-A5C3-B046-ADA3-A32F27508627}" uniqueName="2" name="Check_In_Date" queryTableFieldId="2" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{9C640707-0896-2C4E-B912-C7198DB41FE0}" uniqueName="1" name="Booking_ID" queryTableFieldId="1" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{0FAAFBDC-A5C3-B046-ADA3-A32F27508627}" uniqueName="2" name="Check_In_Date" queryTableFieldId="2" dataDxfId="15"/>
     <tableColumn id="3" xr3:uid="{1327C52C-4C75-2F40-9C92-8BDE6E91562A}" uniqueName="3" name="Room_Number" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{C2DA5368-656F-8A41-B48D-994442019022}" uniqueName="4" name="Room_Type" queryTableFieldId="4" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{72C50A22-907A-FE41-BCB6-44B6648C6E36}" uniqueName="5" name="Booking_Source" queryTableFieldId="5" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{2C0CC303-2AC9-7A47-8AA2-87A358429F1C}" uniqueName="6" name="Guest_Country" queryTableFieldId="6" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{C2DA5368-656F-8A41-B48D-994442019022}" uniqueName="4" name="Room_Type" queryTableFieldId="4" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{72C50A22-907A-FE41-BCB6-44B6648C6E36}" uniqueName="5" name="Booking_Source" queryTableFieldId="5" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{2C0CC303-2AC9-7A47-8AA2-87A358429F1C}" uniqueName="6" name="Guest_Country" queryTableFieldId="6" dataDxfId="12"/>
     <tableColumn id="7" xr3:uid="{71F1C394-3459-9E4D-92A8-C6F7F33105C6}" uniqueName="7" name="Adults" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{A15659F9-EA1C-A14A-A24D-0390AE6E5F7D}" uniqueName="8" name="Nightly_Rate_GBP" queryTableFieldId="8"/>
     <tableColumn id="9" xr3:uid="{E11B8B6A-FBB4-264A-90F3-C0ED4E8C0F2A}" uniqueName="9" name="Resort_Fee_GBP" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{08EA0F62-AA93-504E-96BE-DAB8DD2B70A3}" uniqueName="10" name="Booking_Status" queryTableFieldId="10" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{88B9A17A-26D0-E24F-BB8B-14B648B5A5B0}" uniqueName="11" name="Payment_Status" queryTableFieldId="11" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{08EA0F62-AA93-504E-96BE-DAB8DD2B70A3}" uniqueName="10" name="Booking_Status" queryTableFieldId="10" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{88B9A17A-26D0-E24F-BB8B-14B648B5A5B0}" uniqueName="11" name="Payment_Status" queryTableFieldId="11" dataDxfId="10"/>
     <tableColumn id="12" xr3:uid="{360CD0D5-1EB7-C14D-A1CA-67140092B2FC}" uniqueName="12" name="Guest_Rating" queryTableFieldId="12"/>
-    <tableColumn id="13" xr3:uid="{761F14A1-7736-5C44-806F-446F6EADA4B0}" uniqueName="13" name="Booking_Date" queryTableFieldId="13" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{53076616-DBED-A34A-B53E-7FCD8A40876A}" uniqueName="14" name="Check_Out_Date" queryTableFieldId="14" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{761F14A1-7736-5C44-806F-446F6EADA4B0}" uniqueName="13" name="Booking_Date" queryTableFieldId="13" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{53076616-DBED-A34A-B53E-7FCD8A40876A}" uniqueName="14" name="Check_Out_Date" queryTableFieldId="14" dataDxfId="8"/>
     <tableColumn id="15" xr3:uid="{1AAB83D4-35F6-3A49-83D8-C375F5B7E30B}" uniqueName="15" name="Nights" queryTableFieldId="15"/>
     <tableColumn id="16" xr3:uid="{8C363382-BC03-E346-AA17-2746F4E84D68}" uniqueName="16" name="Estimated_Revenue_GBP" queryTableFieldId="16"/>
   </tableColumns>
@@ -21262,7 +21456,7 @@
   <autoFilter ref="A3:P31" xr:uid="{9F91E32E-1F1C-5241-985E-46C1C890004C}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{FE84019B-EC35-3D4B-941C-451B41A8859B}" name="Booking_ID"/>
-    <tableColumn id="2" xr3:uid="{25B7B310-6F32-AF4A-A94C-857BA435DDB1}" name="Check_In_Date" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{25B7B310-6F32-AF4A-A94C-857BA435DDB1}" name="Check_In_Date" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{AC56E5B3-665B-344B-A650-44EFF7F77DAA}" name="Room_Number"/>
     <tableColumn id="4" xr3:uid="{F41F763D-F72A-7640-8193-222139A13D52}" name="Room_Type"/>
     <tableColumn id="5" xr3:uid="{8BC80606-823F-3E43-8E3E-85F358B09972}" name="Booking_Source"/>
@@ -21273,8 +21467,8 @@
     <tableColumn id="10" xr3:uid="{2CF23607-EEAE-3D4D-B67D-45991345ABD2}" name="Booking_Status"/>
     <tableColumn id="11" xr3:uid="{D283C1E7-4EF5-3C4A-A689-BDDB111F38BA}" name="Payment_Status"/>
     <tableColumn id="12" xr3:uid="{F8764B41-B5EA-4543-B5D0-87EAD3874741}" name="Guest_Rating"/>
-    <tableColumn id="13" xr3:uid="{CC6E2F41-C48C-6843-9EC3-08A79BD2CACF}" name="Booking_Date" dataDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{EB96F629-4F73-4143-9AD3-BE52059CE574}" name="Check_Out_Date" dataDxfId="14"/>
+    <tableColumn id="13" xr3:uid="{CC6E2F41-C48C-6843-9EC3-08A79BD2CACF}" name="Booking_Date" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{EB96F629-4F73-4143-9AD3-BE52059CE574}" name="Check_Out_Date" dataDxfId="5"/>
     <tableColumn id="15" xr3:uid="{608B52E7-01BA-F64C-A011-380B9141335B}" name="Nights"/>
     <tableColumn id="16" xr3:uid="{C1AA6465-E297-4B46-9A07-AB921BA2AC30}" name="Estimated_Revenue_GBP"/>
   </tableColumns>
@@ -21464,7 +21658,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -21472,15 +21666,15 @@
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="40" customHeight="1">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:4" ht="39.950000000000003" customHeight="1">
+      <c r="A1" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-    </row>
-    <row r="3" spans="1:4" ht="16">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+    </row>
+    <row r="3" spans="1:4" ht="15">
       <c r="A3" s="1" t="s">
         <v>168</v>
       </c>
@@ -21494,7 +21688,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15">
+    <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
@@ -21508,7 +21702,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15">
+    <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
@@ -21522,7 +21716,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15">
+    <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
@@ -21536,7 +21730,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15">
+    <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
         <v>3</v>
       </c>
@@ -21550,7 +21744,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15">
+    <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
@@ -21564,7 +21758,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15">
+    <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
         <v>5</v>
       </c>
@@ -21578,7 +21772,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15">
+    <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
         <v>6</v>
       </c>
@@ -21592,7 +21786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15">
+    <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
         <v>7</v>
       </c>
@@ -21606,7 +21800,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15">
+    <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
@@ -21620,7 +21814,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15">
+    <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
@@ -21634,7 +21828,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15">
+    <row r="14" spans="1:4">
       <c r="A14" s="5" t="s">
         <v>10</v>
       </c>
@@ -21648,7 +21842,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15">
+    <row r="15" spans="1:4">
       <c r="A15" s="5" t="s">
         <v>11</v>
       </c>
@@ -21662,7 +21856,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15">
+    <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
         <v>12</v>
       </c>
@@ -21676,7 +21870,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15">
+    <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
         <v>13</v>
       </c>
@@ -21690,9 +21884,9 @@
         <v>199</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="14" customHeight="1"/>
-    <row r="20" spans="1:4" ht="14" customHeight="1">
-      <c r="A20" s="39"/>
+    <row r="19" spans="1:4" ht="14.1" customHeight="1"/>
+    <row r="20" spans="1:4" ht="14.1" customHeight="1">
+      <c r="A20" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -21708,10 +21902,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439F6BFD-EC61-1045-97C0-98F0A3432165}">
   <dimension ref="A3:B9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -21727,7 +21921,7 @@
       <c r="A4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="72">
         <v>30</v>
       </c>
     </row>
@@ -21735,7 +21929,7 @@
       <c r="A5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="72">
         <v>28</v>
       </c>
     </row>
@@ -21743,7 +21937,7 @@
       <c r="A6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="72">
         <v>30</v>
       </c>
     </row>
@@ -21751,7 +21945,7 @@
       <c r="A7" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="72">
         <v>3</v>
       </c>
     </row>
@@ -21759,7 +21953,7 @@
       <c r="A8" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="72">
         <v>29</v>
       </c>
     </row>
@@ -21767,7 +21961,7 @@
       <c r="A9" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="72">
         <v>120</v>
       </c>
     </row>
@@ -21779,10 +21973,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E587F7C1-A4D7-014F-A0E7-DAC3D717A50A}">
   <dimension ref="A3:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:2">
@@ -21797,7 +21991,7 @@
       <c r="A4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="72">
         <v>14</v>
       </c>
     </row>
@@ -21805,7 +21999,7 @@
       <c r="A5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="72">
         <v>98</v>
       </c>
     </row>
@@ -21813,7 +22007,7 @@
       <c r="A6" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="72">
         <v>8</v>
       </c>
     </row>
@@ -21821,7 +22015,7 @@
       <c r="A7" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="72">
         <v>120</v>
       </c>
     </row>
@@ -21833,10 +22027,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D20E5297-D832-414B-92FD-5F5B28D1E561}">
   <dimension ref="A3:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:2">
@@ -21851,7 +22045,7 @@
       <c r="A4" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="72">
         <v>2086.31</v>
       </c>
     </row>
@@ -21859,7 +22053,7 @@
       <c r="A5" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="72">
         <v>2022.94</v>
       </c>
     </row>
@@ -21867,7 +22061,7 @@
       <c r="A6" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="72">
         <v>1855.21</v>
       </c>
     </row>
@@ -21875,7 +22069,7 @@
       <c r="A7" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="72">
         <v>1166.69</v>
       </c>
     </row>
@@ -21883,7 +22077,7 @@
       <c r="A8" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="72">
         <v>2323.92</v>
       </c>
     </row>
@@ -21891,7 +22085,7 @@
       <c r="A9" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="72">
         <v>1336.26</v>
       </c>
     </row>
@@ -21899,7 +22093,7 @@
       <c r="A10" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="72">
         <v>1502.27</v>
       </c>
     </row>
@@ -21907,7 +22101,7 @@
       <c r="A11" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="72">
         <v>2993.44</v>
       </c>
     </row>
@@ -21915,7 +22109,7 @@
       <c r="A12" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="72">
         <v>2455.7600000000002</v>
       </c>
     </row>
@@ -21923,7 +22117,7 @@
       <c r="A13" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="72">
         <v>4162.18</v>
       </c>
     </row>
@@ -21931,7 +22125,7 @@
       <c r="A14" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="72">
         <v>3293.11</v>
       </c>
     </row>
@@ -21939,7 +22133,7 @@
       <c r="A15" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="72">
         <v>3576.46</v>
       </c>
     </row>
@@ -21947,7 +22141,7 @@
       <c r="A16" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="72">
         <v>28774.550000000003</v>
       </c>
     </row>
@@ -21967,10 +22161,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AC76225-769B-7B42-B06D-6E73D59A1F63}">
   <dimension ref="A3:B9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:2">
@@ -22037,21 +22231,21 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A92A7644-D1E0-F540-AE61-8D5F58FB31F6}">
   <dimension ref="A1:P31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="26.5" bestFit="1" customWidth="1"/>
@@ -22059,7 +22253,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="15">
       <c r="A1" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -23505,7 +23699,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F92D576-0259-B241-A9CB-5C2667FDB10E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -23515,7 +23709,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N124"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="4" width="15" customWidth="1"/>
@@ -23529,7 +23723,7 @@
     <col min="14" max="14" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="45.25" customHeight="1">
+    <row r="1" spans="1:14" ht="45.2" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -28919,20 +29113,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A0EE6F-E220-8946-B9DF-20BBCCB8CDD4}">
   <dimension ref="A1:R121"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.875" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="18" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="26.5" bestFit="1" customWidth="1"/>
@@ -34955,9 +35149,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70CA42EE-81C4-7A4E-947B-CDF616D1F73B}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="1" max="1" width="25.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -35044,144 +35238,937 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71D97ED4-2C8B-2947-B24D-EF8418ABDCAE}">
-  <dimension ref="A1:O6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:T40"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="20" width="9.625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-    </row>
-    <row r="4" spans="1:15" ht="15">
-      <c r="A4" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-    </row>
-    <row r="5" spans="1:15" ht="14" customHeight="1">
+    <row r="1" spans="1:20" ht="33.950000000000003" customHeight="1">
+      <c r="A1" s="29" t="s">
+        <v>344</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+    </row>
+    <row r="2" spans="1:20" ht="21.95" customHeight="1">
+      <c r="A2" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+    </row>
+    <row r="3" spans="1:20" ht="9.9499999999999993" customHeight="1">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+    </row>
+    <row r="4" spans="1:20" ht="32.1" customHeight="1">
+      <c r="A4" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="B4" s="40"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="22" t="s">
+        <v>347</v>
+      </c>
+      <c r="E4" s="47"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="H4" s="40"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="K4" s="59"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="N4" s="47"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="32" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q4" s="71"/>
+      <c r="R4" s="71"/>
+      <c r="S4" s="71"/>
+      <c r="T4" s="71"/>
+    </row>
+    <row r="5" spans="1:20" ht="27.95" customHeight="1">
       <c r="A5" s="25">
         <f>Pivot_KPI!A2</f>
         <v>28774.549999999996</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="31">
+      <c r="B5" s="42"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="26">
         <f>Pivot_KPI!D2</f>
         <v>120</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="32">
+      <c r="E5" s="49"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="27">
         <f>Pivot_KPI!G4</f>
         <v>98</v>
       </c>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="17">
+      <c r="H5" s="54"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="21">
         <f>IFERROR(Pivot_KPI!J4/Pivot_KPI!D2,0)</f>
         <v>0.11666666666666667</v>
       </c>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="19">
+      <c r="K5" s="61"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="23">
         <f>Pivot_KPI!M2</f>
         <v>4.1530612244897958</v>
       </c>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-    </row>
-    <row r="6" spans="1:15" ht="14" customHeight="1">
-      <c r="A6" s="28"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="19"/>
+    </row>
+    <row r="6" spans="1:20" ht="9" customHeight="1">
+      <c r="A6" s="44"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+    </row>
+    <row r="7" spans="1:20" ht="9.9499999999999993" customHeight="1">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
+    </row>
+    <row r="8" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="19"/>
+    </row>
+    <row r="9" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+    </row>
+    <row r="10" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+    </row>
+    <row r="11" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+    </row>
+    <row r="12" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+    </row>
+    <row r="13" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+    </row>
+    <row r="14" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+    </row>
+    <row r="15" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="19"/>
+    </row>
+    <row r="16" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+    </row>
+    <row r="17" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="19"/>
+    </row>
+    <row r="18" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="19"/>
+    </row>
+    <row r="19" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="19"/>
+    </row>
+    <row r="20" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="19"/>
+    </row>
+    <row r="21" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="19"/>
+      <c r="T21" s="19"/>
+    </row>
+    <row r="22" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="19"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="19"/>
+    </row>
+    <row r="23" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="19"/>
+    </row>
+    <row r="24" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="19"/>
+    </row>
+    <row r="25" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+    </row>
+    <row r="26" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+    </row>
+    <row r="27" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+    </row>
+    <row r="28" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+    </row>
+    <row r="29" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+    </row>
+    <row r="30" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+    </row>
+    <row r="31" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="19"/>
+      <c r="S31" s="19"/>
+      <c r="T31" s="19"/>
+    </row>
+    <row r="32" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="19"/>
+      <c r="S32" s="19"/>
+      <c r="T32" s="19"/>
+    </row>
+    <row r="33" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="19"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="19"/>
+    </row>
+    <row r="34" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="19"/>
+      <c r="S34" s="19"/>
+      <c r="T34" s="19"/>
+    </row>
+    <row r="35" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A35" s="19"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
+      <c r="O35" s="19"/>
+      <c r="P35" s="19"/>
+      <c r="Q35" s="19"/>
+      <c r="R35" s="19"/>
+      <c r="S35" s="19"/>
+      <c r="T35" s="19"/>
+    </row>
+    <row r="36" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A36" s="19"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="19"/>
+      <c r="O36" s="19"/>
+      <c r="P36" s="19"/>
+      <c r="Q36" s="19"/>
+      <c r="R36" s="19"/>
+      <c r="S36" s="19"/>
+      <c r="T36" s="19"/>
+    </row>
+    <row r="37" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A37" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="39"/>
+      <c r="L37" s="39"/>
+      <c r="M37" s="39"/>
+      <c r="N37" s="39"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="19"/>
+      <c r="Q37" s="19"/>
+      <c r="R37" s="19"/>
+      <c r="S37" s="19"/>
+      <c r="T37" s="19"/>
+    </row>
+    <row r="38" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A38" s="39"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="39"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="39"/>
+      <c r="M38" s="39"/>
+      <c r="N38" s="39"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="19"/>
+      <c r="R38" s="19"/>
+      <c r="S38" s="19"/>
+      <c r="T38" s="19"/>
+    </row>
+    <row r="39" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A39" s="19"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="19"/>
+      <c r="R39" s="19"/>
+      <c r="S39" s="19"/>
+      <c r="T39" s="19"/>
+    </row>
+    <row r="40" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A40" s="19"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="19"/>
+      <c r="R40" s="19"/>
+      <c r="S40" s="19"/>
+      <c r="T40" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="14">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="P4:T4"/>
+    <mergeCell ref="A37:O38"/>
     <mergeCell ref="J5:L6"/>
     <mergeCell ref="M4:O4"/>
     <mergeCell ref="M5:O6"/>
-    <mergeCell ref="A1:O3"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A5:C6"/>
     <mergeCell ref="D4:F4"/>
@@ -35190,17 +36177,19 @@
     <mergeCell ref="G5:I6"/>
     <mergeCell ref="J4:L4"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.1111111111111111" right="0.1111111111111111" top="0.1111111111111111" bottom="0.1111111111111111" header="0.3" footer="0.3"/>
+  <pageSetup scale="65" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId2"/>
+        <x14:slicer r:id="rId3"/>
       </x14:slicerList>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{7E03D99C-DC04-49d9-9315-930204A7B6E9}">
       <x15:timelineRefs>
-        <x15:timelineRef r:id="rId3"/>
+        <x15:timelineRef r:id="rId4"/>
       </x15:timelineRefs>
     </ext>
   </extLst>
@@ -35210,242 +36199,242 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E40BE785-1353-A24F-8D02-201CCAA3D8AC}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
     <col min="10" max="10" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+    </row>
+    <row r="3" spans="1:8" ht="30" customHeight="1">
+      <c r="A3" s="35" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-    </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1">
-      <c r="A3" s="34" t="s">
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+    </row>
+    <row r="4" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A4" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+    </row>
+    <row r="5" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A5" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+    </row>
+    <row r="6" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A6" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+    </row>
+    <row r="7" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A7" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+    </row>
+    <row r="8" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A8" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+    </row>
+    <row r="9" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A9" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+    </row>
+    <row r="10" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A10" s="36" t="s">
+        <v>239</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+    </row>
+    <row r="11" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A11" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+    </row>
+    <row r="12" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A12" s="36" t="s">
         <v>232</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-    </row>
-    <row r="4" spans="1:8" ht="25" customHeight="1">
-      <c r="A4" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-    </row>
-    <row r="5" spans="1:8" ht="25" customHeight="1">
-      <c r="A5" s="35" t="s">
-        <v>235</v>
-      </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-    </row>
-    <row r="6" spans="1:8" ht="25" customHeight="1">
-      <c r="A6" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-    </row>
-    <row r="7" spans="1:8" ht="25" customHeight="1">
-      <c r="A7" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-    </row>
-    <row r="8" spans="1:8" ht="25" customHeight="1">
-      <c r="A8" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-    </row>
-    <row r="9" spans="1:8" ht="25" customHeight="1">
-      <c r="A9" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-    </row>
-    <row r="10" spans="1:8" ht="25" customHeight="1">
-      <c r="A10" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-    </row>
-    <row r="11" spans="1:8" ht="25" customHeight="1">
-      <c r="A11" s="35" t="s">
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+    </row>
+    <row r="13" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A13" s="36" t="s">
         <v>241</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-    </row>
-    <row r="12" spans="1:8" ht="25" customHeight="1">
-      <c r="A12" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-    </row>
-    <row r="13" spans="1:8" ht="25" customHeight="1">
-      <c r="A13" s="35" t="s">
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+    </row>
+    <row r="15" spans="1:8" ht="30" customHeight="1">
+      <c r="A15" s="37" t="s">
         <v>242</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-    </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1">
-      <c r="A15" s="36" t="s">
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+    </row>
+    <row r="16" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A16" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-    </row>
-    <row r="16" spans="1:8" ht="25" customHeight="1">
-      <c r="A16" s="33" t="s">
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+    </row>
+    <row r="17" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A17" s="34" t="s">
         <v>244</v>
       </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-    </row>
-    <row r="17" spans="1:8" ht="25" customHeight="1">
-      <c r="A17" s="33" t="s">
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+    </row>
+    <row r="18" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A18" s="34" t="s">
         <v>245</v>
       </c>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-    </row>
-    <row r="18" spans="1:8" ht="25" customHeight="1">
-      <c r="A18" s="33" t="s">
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+    </row>
+    <row r="19" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A19" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-    </row>
-    <row r="19" spans="1:8" ht="25" customHeight="1">
-      <c r="A19" s="33" t="s">
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+    </row>
+    <row r="20" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A20" s="34" t="s">
         <v>247</v>
       </c>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-    </row>
-    <row r="20" spans="1:8" ht="25" customHeight="1">
-      <c r="A20" s="33" t="s">
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+    </row>
+    <row r="21" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A21" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-    </row>
-    <row r="21" spans="1:8" ht="25" customHeight="1">
-      <c r="A21" s="33" t="s">
-        <v>249</v>
-      </c>
-      <c r="B21" s="33"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -35477,48 +36466,48 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F243C1B-2311-B44F-819A-A3C2B592138B}">
   <dimension ref="A1:K29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="20.1640625" customWidth="1"/>
-    <col min="2" max="2" width="52.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.1640625" customWidth="1"/>
+    <col min="1" max="1" width="20.125" customWidth="1"/>
+    <col min="2" max="2" width="52.875" customWidth="1"/>
+    <col min="3" max="3" width="16.125" customWidth="1"/>
     <col min="4" max="4" width="69.5" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B1" t="s">
         <v>251</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>252</v>
-      </c>
-      <c r="C1" t="s">
-        <v>253</v>
       </c>
       <c r="D1" t="s">
         <v>169</v>
       </c>
       <c r="E1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B2" t="s">
         <v>254</v>
-      </c>
-      <c r="B2" t="s">
-        <v>255</v>
       </c>
       <c r="C2" s="13">
         <f>SUMIF(Cleaned_Motel_Data[Room_Type],"Deluxe",Cleaned_Motel_Data[Estimated_Revenue_GBP])</f>
         <v>7366.9</v>
       </c>
       <c r="D2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E2">
         <v>7000</v>
@@ -35527,7 +36516,7 @@
         <v>64</v>
       </c>
       <c r="H2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J2" t="s">
         <v>51</v>
@@ -35535,41 +36524,41 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C3" s="13">
         <f>SUMIFS(Cleaned_Motel_Data[Estimated_Revenue_GBP],Cleaned_Motel_Data[Booking_Status],"Completed",Cleaned_Motel_Data[Booking_Source],"Booking.com")</f>
         <v>7358.8</v>
       </c>
       <c r="D3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C4">
         <f>COUNTIFS(Cleaned_Motel_Data[Booking_Status],"Completed",Cleaned_Motel_Data[Room_Type],"Deluxe")</f>
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K4">
         <v>100</v>
@@ -35577,17 +36566,17 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B5" t="s">
         <v>263</v>
-      </c>
-      <c r="B5" t="s">
-        <v>264</v>
       </c>
       <c r="C5" s="10">
         <f>AVERAGEIF(Cleaned_Motel_Data[Room_Type],"Deluxe",Cleaned_Motel_Data[Guest_Rating])</f>
         <v>4.333333333333333</v>
       </c>
       <c r="D5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H5" t="s">
         <v>73</v>
@@ -35601,23 +36590,23 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B6" t="s">
         <v>266</v>
-      </c>
-      <c r="B6" t="s">
-        <v>267</v>
       </c>
       <c r="C6" s="13">
         <f>AVERAGEIFS(Cleaned_Motel_Data[Nightly_Rate_GBP],Cleaned_Motel_Data[Booking_Status],"Completed",Cleaned_Motel_Data[Room_Type],"Deluxe")</f>
         <v>109.0275</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H6" t="s">
         <v>50</v>
       </c>
       <c r="J6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K6">
         <f>K4*K5</f>
@@ -35626,17 +36615,17 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
+        <v>268</v>
+      </c>
+      <c r="B7" t="s">
         <v>269</v>
-      </c>
-      <c r="B7" t="s">
-        <v>270</v>
       </c>
       <c r="C7" s="13">
         <f>MIN(Cleaned_Motel_Data[Nightly_Rate_GBP])</f>
         <v>71.72</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H7" s="16">
         <f>DATE(2025,8,5)</f>
@@ -35645,17 +36634,17 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
+        <v>271</v>
+      </c>
+      <c r="B8" t="s">
         <v>272</v>
-      </c>
-      <c r="B8" t="s">
-        <v>273</v>
       </c>
       <c r="C8" s="13">
         <f>MAX(Cleaned_Motel_Data[Nightly_Rate_GBP])</f>
         <v>144.44999999999999</v>
       </c>
       <c r="D8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H8" s="16">
         <f>DATE(2025,8,10)</f>
@@ -35664,317 +36653,317 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B9" t="s">
         <v>275</v>
-      </c>
-      <c r="B9" t="s">
-        <v>276</v>
       </c>
       <c r="C9" s="13">
         <f>ROUND(AVERAGE(Cleaned_Motel_Data[Nightly_Rate_GBP]),2)</f>
         <v>103.81</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
+        <v>277</v>
+      </c>
+      <c r="B10" t="s">
         <v>278</v>
-      </c>
-      <c r="B10" t="s">
-        <v>279</v>
       </c>
       <c r="C10" t="str">
         <f>IF(COUNTIF(Cleaned_Motel_Data[Booking_Status],"Cancelled")&gt;10,"High Cancellations","Low Cancellations")</f>
         <v>High Cancellations</v>
       </c>
       <c r="D10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
+        <v>279</v>
+      </c>
+      <c r="B11" t="s">
         <v>280</v>
-      </c>
-      <c r="B11" t="s">
-        <v>281</v>
       </c>
       <c r="C11" t="str" cm="1">
         <f t="array" ref="C11">_xlfn.IFS(C2&gt;=7500,"Excellent",C2&gt;=6500,"Good",TRUE,"Needs Attention")</f>
         <v>Good</v>
       </c>
       <c r="D11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C12" t="str">
         <f>IF(C2&gt;=$E$2,"Target Met","Below Target")</f>
         <v>Target Met</v>
       </c>
       <c r="D12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
+        <v>287</v>
+      </c>
+      <c r="B13" t="s">
         <v>288</v>
-      </c>
-      <c r="B13" t="s">
-        <v>289</v>
       </c>
       <c r="C13" t="str">
         <f>_xlfn.XLOOKUP(F2,Cleaned_Motel_Data[Booking_ID],Cleaned_Motel_Data[Room_Type])</f>
         <v>Deluxe</v>
       </c>
       <c r="D13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
+        <v>290</v>
+      </c>
+      <c r="B14" t="s">
         <v>291</v>
-      </c>
-      <c r="B14" t="s">
-        <v>292</v>
       </c>
       <c r="C14" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F2,Cleaned_Motel_Data[Booking_ID],Cleaned_Motel_Data[Room_Type]),"Booking ID Not Found")</f>
         <v>Deluxe</v>
       </c>
       <c r="D14" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.75">
+      <c r="A15" s="15" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="16">
-      <c r="A15" s="15" t="s">
-        <v>294</v>
-      </c>
       <c r="B15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C15" t="str">
         <f>TRIM(H2)</f>
         <v>deluxe</v>
       </c>
       <c r="D15" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="16">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15.75">
       <c r="A16" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C16" t="str">
         <f>PROPER(H3)</f>
         <v>Deluxe Room</v>
       </c>
       <c r="D16" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="16">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75">
       <c r="A17" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C17" t="str">
         <f>UPPER(H4)</f>
         <v>BOOKING.COM</v>
       </c>
       <c r="D17" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="16">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75">
       <c r="A18" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C18" t="str">
         <f>LOWER(H5)</f>
         <v>booking.com</v>
       </c>
       <c r="D18" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75">
+      <c r="A19" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="B19" t="s">
         <v>314</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="16">
-      <c r="A19" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="B19" t="s">
-        <v>315</v>
       </c>
       <c r="C19" t="str">
         <f>LEFT(F2,2)</f>
         <v>BK</v>
       </c>
       <c r="D19" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="16">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75">
       <c r="A20" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B20" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C20" t="str">
         <f>RIGHT(F2,4)</f>
         <v>1026</v>
       </c>
       <c r="D20" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75">
+      <c r="A21" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="B21" t="s">
         <v>318</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="16">
-      <c r="A21" s="15" t="s">
-        <v>300</v>
-      </c>
-      <c r="B21" t="s">
-        <v>319</v>
       </c>
       <c r="C21" t="str">
         <f>MID(F2,3,4)</f>
         <v>1026</v>
       </c>
       <c r="D21" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75">
+      <c r="A22" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="B22" t="s">
         <v>320</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="16">
-      <c r="A22" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="B22" t="s">
-        <v>321</v>
       </c>
       <c r="C22">
         <f>LEN(F2)</f>
         <v>6</v>
       </c>
       <c r="D22" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75">
+      <c r="A23" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="B23" t="s">
         <v>322</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="16">
-      <c r="A23" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="B23" t="s">
-        <v>323</v>
       </c>
       <c r="C23" t="str">
         <f>_xlfn.CONCAT(F2," - ",C13)</f>
         <v>BK1026 - Deluxe</v>
       </c>
       <c r="D23" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75">
+      <c r="A24" s="15" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="16">
-      <c r="A24" s="15" t="s">
-        <v>325</v>
-      </c>
       <c r="B24" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C24">
         <f>YEAR(H7)</f>
         <v>2025</v>
       </c>
       <c r="D24" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75">
+      <c r="A25" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="B25" t="s">
         <v>332</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="16">
-      <c r="A25" s="15" t="s">
-        <v>326</v>
-      </c>
-      <c r="B25" t="s">
-        <v>333</v>
       </c>
       <c r="C25">
         <f>MONTH(H7)</f>
         <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="16">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75">
       <c r="A26" s="15" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B26" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C26">
         <f>DAY(H7)</f>
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="16">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75">
       <c r="A27" s="15" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B27" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C27" s="16">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46322</v>
       </c>
       <c r="D27" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="16">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75">
       <c r="A28" s="15" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B28" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C28">
         <f>DATEDIF(H7,H8,"d")</f>
         <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="16">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.75">
       <c r="A29" s="15" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B29" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C29">
         <f>EOMONTH(H7,0)</f>
         <v>45900</v>
       </c>
       <c r="D29" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -35985,15 +36974,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7DF77AF-F63D-BC47-B497-4EB30BAACD0A}">
   <dimension ref="A1:M4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="32.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -36020,10 +37009,10 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2">
+      <c r="A2" s="72">
         <v>28774.549999999996</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="72">
         <v>120</v>
       </c>
       <c r="M2" s="10">
@@ -36039,10 +37028,10 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="G4">
+      <c r="G4" s="72">
         <v>98</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="72">
         <v>14</v>
       </c>
     </row>
@@ -36054,10 +37043,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC57505F-7CB8-C241-A6DA-2F98A5D1E3D8}">
   <dimension ref="A3:B9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:2">
